--- a/Result/profitability/2471.xlsx
+++ b/Result/profitability/2471.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7575000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>39.13</v>
+        <v>38.98375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.64</v>
+        <v>0.5887500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>36.54499999999999</v>
+        <v>36.81375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.43</v>
+        <v>0.5325000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>34.06125</v>
+        <v>35.815</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3462499999999999</v>
+        <v>0.4725</v>
       </c>
       <c r="N5" t="n">
-        <v>31.4</v>
+        <v>31.875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3425</v>
+        <v>0.3174999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>29.83125</v>
+        <v>29.31625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.18375</v>
+        <v>0.08125</v>
       </c>
       <c r="N7" t="n">
-        <v>27.68375</v>
+        <v>27.12875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.19</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03375</v>
+        <v>0.04375000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>24.21875</v>
+        <v>25.91875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2471</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>243</v>
+      </c>
+      <c r="D75" t="n">
+        <v>134</v>
+      </c>
+      <c r="E75" t="n">
+        <v>109</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="G75" t="n">
+        <v>48</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>56</v>
+      </c>
+      <c r="K75" t="n">
+        <v>52</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.75875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6200000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.26530612244898</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4367373153500322</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.800000000000004</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.09281875915974602</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
